--- a/AAII_Financials/Quarterly/KG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KG_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="92">
   <si>
     <t>KG</t>
   </si>
@@ -656,59 +656,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="19" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
@@ -733,35 +734,38 @@
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>10200</v>
+        <v>6700</v>
       </c>
       <c r="E8" s="3">
         <v>10200</v>
       </c>
       <c r="F8" s="3">
+        <v>10200</v>
+      </c>
+      <c r="G8" s="3">
         <v>17400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>5600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>800</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
@@ -786,26 +790,29 @@
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2500</v>
+      </c>
+      <c r="E9" s="3">
         <v>3700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>-5600</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -839,35 +846,38 @@
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E10" s="3">
         <v>6500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
@@ -892,8 +902,11 @@
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -913,8 +926,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -966,8 +980,11 @@
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1019,25 +1036,28 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>700</v>
+        <v>-200</v>
       </c>
       <c r="E14" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F14" s="3">
         <v>9800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-800</v>
       </c>
-      <c r="G14" s="3">
-        <v>-69200</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
+      <c r="H14" s="3">
+        <v>-69000</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
@@ -1072,8 +1092,11 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1104,8 +1127,8 @@
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>3</v>
+      <c r="M15" s="3">
+        <v>0</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>3</v>
@@ -1125,8 +1148,11 @@
       <c r="S15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1143,35 +1169,36 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14800</v>
+        <v>13200</v>
       </c>
       <c r="E17" s="3">
+        <v>16200</v>
+      </c>
+      <c r="F17" s="3">
         <v>13100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>21000</v>
       </c>
-      <c r="G17" s="3">
-        <v>-2200</v>
-      </c>
       <c r="H17" s="3">
-        <v>1100</v>
+        <v>-2000</v>
       </c>
       <c r="I17" s="3">
         <v>1100</v>
       </c>
       <c r="J17" s="3">
+        <v>1100</v>
+      </c>
+      <c r="K17" s="3">
         <v>1200</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1196,35 +1223,38 @@
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-4600</v>
+        <v>-6500</v>
       </c>
       <c r="E18" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="F18" s="3">
         <v>-2900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3600</v>
       </c>
-      <c r="G18" s="3">
-        <v>7700</v>
-      </c>
       <c r="H18" s="3">
+        <v>7500</v>
+      </c>
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-400</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1249,8 +1279,11 @@
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1270,25 +1303,26 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3500</v>
       </c>
-      <c r="G20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
+      <c r="H20" s="3">
+        <v>4800</v>
       </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
@@ -1323,40 +1357,43 @@
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-1500</v>
+        <v>-3600</v>
       </c>
       <c r="E21" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F21" s="3">
         <v>-2000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-100</v>
       </c>
-      <c r="G21" s="3">
-        <v>3000</v>
-      </c>
       <c r="H21" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I21" s="3">
         <v>-300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-400</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
       <c r="L21" s="3">
         <v>0</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
+      <c r="M21" s="3">
+        <v>0</v>
       </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
@@ -1376,8 +1413,11 @@
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1385,17 +1425,17 @@
         <v>4800</v>
       </c>
       <c r="E22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F22" s="3">
         <v>4700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1800</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1429,35 +1469,38 @@
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-6900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-16400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-4100</v>
       </c>
-      <c r="G23" s="3">
-        <v>70400</v>
-      </c>
       <c r="H23" s="3">
+        <v>69900</v>
+      </c>
+      <c r="I23" s="3">
         <v>-300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-400</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,13 +1525,16 @@
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1500,13 +1546,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1535,8 +1581,11 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1588,35 +1637,38 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-7000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-16400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
-        <v>70400</v>
-      </c>
       <c r="H26" s="3">
+        <v>69900</v>
+      </c>
+      <c r="I26" s="3">
         <v>-400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-400</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1641,35 +1693,38 @@
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-7400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-17900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>69700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-400</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,8 +1749,11 @@
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1747,23 +1805,26 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
         <v>-500</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1400</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1000</v>
       </c>
-      <c r="G29" s="3">
-        <v>-500</v>
-      </c>
       <c r="H29" s="3">
         <v>0</v>
       </c>
@@ -1779,8 +1840,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>3</v>
@@ -1800,8 +1861,11 @@
       <c r="S29" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1853,8 +1917,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1906,25 +1973,28 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
+      <c r="H32" s="3">
+        <v>-4800</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
@@ -1959,35 +2029,38 @@
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-7400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-17800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>69900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-400</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2012,8 +2085,11 @@
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2065,35 +2141,38 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-7400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-17800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>69900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-400</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2118,40 +2197,43 @@
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2176,8 +2258,11 @@
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2197,8 +2282,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2218,32 +2304,33 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>16100</v>
+      </c>
+      <c r="E41" s="3">
         <v>15100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4300</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2271,8 +2358,11 @@
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2303,8 +2393,8 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
+      <c r="M42" s="3">
+        <v>0</v>
       </c>
       <c r="N42" s="3" t="s">
         <v>3</v>
@@ -2324,32 +2414,35 @@
       <c r="S42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E43" s="3">
         <v>3100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2377,8 +2470,11 @@
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2430,26 +2526,29 @@
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>429000</v>
+      </c>
+      <c r="E45" s="3">
         <v>457900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>497300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>538700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>567800</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2483,32 +2582,35 @@
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>459200</v>
+      </c>
+      <c r="E46" s="3">
         <v>523300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>516800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>580800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>602800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5300</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2536,26 +2638,29 @@
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>363100</v>
+      </c>
+      <c r="E47" s="3">
         <v>339300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>381800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>414300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>412300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,31 +2694,34 @@
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>2000</v>
+        <v>1900</v>
       </c>
       <c r="E48" s="3">
         <v>2000</v>
       </c>
       <c r="F48" s="3">
+        <v>2000</v>
+      </c>
+      <c r="G48" s="3">
         <v>2100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1600</v>
-      </c>
-      <c r="H48" s="3">
-        <v>200</v>
       </c>
       <c r="I48" s="3">
         <v>200</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>3</v>
+      <c r="J48" s="3">
+        <v>200</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>3</v>
@@ -2642,34 +2750,37 @@
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E49" s="3">
         <v>8500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>9300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11400</v>
       </c>
-      <c r="H49" s="3">
-        <v>0</v>
-      </c>
       <c r="I49" s="3">
         <v>0</v>
       </c>
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2695,8 +2806,11 @@
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2748,8 +2862,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2801,31 +2918,34 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E52" s="3">
         <v>12500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>23900</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="I52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J52" s="3">
+        <v>0</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2854,8 +2974,11 @@
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2907,32 +3030,35 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>919600</v>
+      </c>
+      <c r="E54" s="3">
         <v>964200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1010000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1130400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1159400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>4900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5500</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2960,8 +3086,11 @@
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2981,8 +3110,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3002,8 +3132,9 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3019,12 +3150,12 @@
       <c r="G57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3">
         <v>200</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3055,34 +3186,37 @@
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>200</v>
+      </c>
+      <c r="E58" s="3">
         <v>300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>100</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
+      <c r="K58" s="3">
+        <v>0</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
@@ -3108,26 +3242,29 @@
       <c r="S58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E59" s="3">
         <v>21300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>22500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27100</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3161,32 +3298,35 @@
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>74500</v>
+      </c>
+      <c r="E60" s="3">
         <v>73000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>68400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>121200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>100400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>700</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3214,40 +3354,43 @@
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>176800</v>
+      </c>
+      <c r="E61" s="3">
         <v>176400</v>
-      </c>
-      <c r="E61" s="3">
-        <v>176100</v>
       </c>
       <c r="F61" s="3">
         <v>176100</v>
       </c>
       <c r="G61" s="3">
+        <v>176100</v>
+      </c>
+      <c r="H61" s="3">
         <v>175800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>200</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3" t="s">
-        <v>3</v>
+      <c r="M61" s="3">
+        <v>0</v>
       </c>
       <c r="N61" s="3" t="s">
         <v>3</v>
@@ -3267,26 +3410,29 @@
       <c r="S61" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>554300</v>
+      </c>
+      <c r="E62" s="3">
         <v>593400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>637200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>689400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>733100</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3320,8 +3466,11 @@
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3373,8 +3522,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3426,8 +3578,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3479,32 +3634,35 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>805600</v>
+      </c>
+      <c r="E66" s="3">
         <v>842800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>881700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>986700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1009300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>900</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3532,8 +3690,11 @@
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3553,8 +3714,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3606,8 +3768,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3659,8 +3824,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3691,8 +3859,8 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3" t="s">
-        <v>3</v>
+      <c r="M70" s="3">
+        <v>0</v>
       </c>
       <c r="N70" s="3" t="s">
         <v>3</v>
@@ -3712,8 +3880,11 @@
       <c r="S70" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3765,32 +3936,35 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-6200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>19000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>24000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-5900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-5500</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3818,8 +3992,11 @@
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3871,8 +4048,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3924,8 +4104,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3977,32 +4160,35 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E76" s="3">
         <v>121400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>128300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>143800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>150100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4600</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4030,8 +4216,11 @@
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4083,40 +4272,43 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4141,35 +4333,38 @@
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-7400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-17800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>69900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-400</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
@@ -4194,8 +4389,11 @@
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4215,8 +4413,9 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4268,8 +4467,11 @@
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4321,8 +4523,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4374,8 +4579,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4427,8 +4635,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4480,8 +4691,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4533,35 +4747,38 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-15100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-65700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-9700</v>
       </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4586,8 +4803,11 @@
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4607,8 +4827,9 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4660,8 +4881,11 @@
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4713,8 +4937,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4766,25 +4993,28 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13800</v>
+      </c>
+      <c r="E94" s="3">
         <v>53000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>42500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>16100</v>
       </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
+      <c r="H94" s="3">
+        <v>102000</v>
       </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
@@ -4819,8 +5049,11 @@
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4840,25 +5073,26 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E96" s="3">
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3">
         <v>40000</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>3</v>
+      <c r="H96" s="3">
+        <v>40000</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>3</v>
@@ -4893,8 +5127,11 @@
       <c r="S96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4946,8 +5183,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4999,8 +5239,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5052,25 +5295,28 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
         <v>-500</v>
       </c>
-      <c r="E100" s="3">
-        <v>0</v>
-      </c>
       <c r="F100" s="3">
         <v>0</v>
       </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
+      <c r="G100" s="3">
+        <v>0</v>
+      </c>
+      <c r="H100" s="3">
+        <v>-40000</v>
       </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
@@ -5105,13 +5351,16 @@
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>700</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>3</v>
@@ -5158,40 +5407,43 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-39700</v>
+      </c>
+      <c r="E102" s="3">
         <v>36800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-23300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6200</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>42800</v>
+      </c>
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
         <v>0</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
+      <c r="M102" s="3">
+        <v>0</v>
       </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
@@ -5209,6 +5461,9 @@
         <v>3</v>
       </c>
       <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
